--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_012/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_012/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -505,11 +510,6 @@
       </text>
     </comment>
     <comment ref="F6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>FUN3D steady RANS predictions of CL/CD and surface Cp for CRM wing-body transonic aero loads envelope</t>
+          <t>FUN3D RANS/IDDES predictions of CL, CD, and surface Cp for NASA CRM wing-body at transonic conditions to support aero loads envelope</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Use FUN3D 13.8 compressible RANS (k-ω SST) predictions of mean lift coefficient, drag coefficient, and sectional surface pressure distributions for the NASA Common Research Model wing-body at M=0.72–0.90, α=0–4 deg, Re=3–8 million to support structural loads envelope sizing. Decision tolerances: ≤±1.5% on CL, ≤±8 drag counts on CD, shock location within ±0.02c, Cp RMS within ±5% at tap rows.</t>
+          <t>Steady compressible RANS (k-ω SST) and limited IDDES simulations of the NASA Common Research Model wing-body at M=0.72–0.90, α=0–4 deg, Re=3–8 million. Predictions of mean CL, CD, sectional Cp, and shock position are used to define the loads envelope for Loads/Structures decisions. Decision tolerances: ≤±1.5% on CL, ≤±8 drag counts on CD, shock location within ±0.02c, Cp RMS within ±5% at tap rows.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1354,9 +1354,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md (M. Rivera to A. Patel, CRM transonic CFD credibility package status memo, 2026-08-06)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Aero Loads Decision Tolerances</t>
+          <t>Loads Envelope Accuracy Requirements</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Model predictions must achieve ≤±1.5% on CL, ≤±8 drag counts on CD, shock location within ±0.02c, and Cp RMS within ±5% at tap rows across the validated envelope (M=0.72–0.90, α=0–4 deg, Re=3–8M) to support the loads envelope.</t>
+          <t>Model predictions must meet agreed decision tolerances: ≤±1.5% on CL, ≤±8 drag counts on CD, shock location within ±0.02c, and Cp RMS within ±5% at tap rows, over the validated envelope M=0.72–0.90, α=0–4 deg, Re=3–8M.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>FUN3D 13.8 Compressible RANS (k-ω SST)</t>
+          <t>FUN3D 13.8 RANS/IDDES</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Steady compressible RANS solver with k-ω SST turbulence model on unstructured grids (12M/34M/96M cells); IDDES used for limited unsteady buffet spot checks at M=0.85, α=3 deg.</t>
+          <t>NASA FUN3D solver v13.8, compressible RANS (steady, k-ω SST) and IDDES (unsteady), double precision, second-order in space and time, run on Pleiades (Skylake) with Intel oneAPI 2023.2 and OpenMPI 4.1.5.</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>NTF CRM Wind Tunnel Campaign (DPW-III/IV lineage)</t>
+          <t>NTF CRM Experimental Campaign</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>National Transonic Facility cryogenic wind tunnel measurements of CL, CD, and Cp for the NASA CRM wing-body; blockage/weight corrections applied per facility procedures; measurement uncertainties: CL ±0.002, CD ±3 counts, Cp taps ±50 Pa, AoA repeatability ±0.02 deg.</t>
+          <t>National Transonic Facility CRM wing-body test data (AIAA DPW-III/IV lineage), cryogenic conditions, with blockage/weight corrections; measurement uncertainties CL ±0.002, CD ±3 counts, Cp taps ±50 Pa, AoA repeatability ±0.02 deg.</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Latin Hypercube Uncertainty Propagation Workbook</t>
+          <t>NASA CRM Wing-Body Geometry (Rev 2)</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>40-point LHS sampling of input uncertainties (α ±0.05 deg, Tu 0.2–1.0%, roughness k+ 0–3) used to generate 95% prediction intervals on CL, CD, and shock position.</t>
+          <t>Watertight surface CAD from LaRC for the NASA CRM wing-body baseline Rev 2; planform and section verified against reference within 0.2 mm.</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Force and Pressure Coefficient Comparison vs. NTF Data</t>
+          <t>Force and Surface Pressure Comparison to NTF Data</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Steady RANS predictions of CL, CD, spanwise shock position, and upper-surface Cp RMS compared against NTF CRM wind tunnel measurements at M=0.85, α=2–4 deg.</t>
+          <t>FUN3D steady RANS predictions compared to NTF CRM experimental data at M=0.85, α=2–4 deg; assessed CL, CD, spanwise shock position, and Cp RMS on upper-surface tap rows.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>NTF CRM campaign experimental data (DPW-III/IV lineage)</t>
+          <t>NTF CRM campaign (DPW-III/IV lineage) experimental measurements</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Measurement uncertainty quoted; 40-point Latin hypercube propagation for prediction intervals</t>
+          <t>Measurement uncertainty characterization (CL ±0.002, CD ±3 counts, Cp taps ±50 Pa); 40-point Latin hypercube propagation of input spreads (α, Tu, roughness); Sobol sensitivity screening</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>CL within 0.8% (tolerance ±1.5%); CD within 6 counts (tolerance ±8 counts); shock x/c within 0.02c (tolerance ±0.02c); Cp RMS within 3–4% (tolerance ±5%)</t>
+          <t>CL within 0.8% of mean; CD within 6 counts; shock x/c within 0.02c; Cp RMS within 3–4% on upper-surface rows; 95% UQ intervals: ±1.2% CL, ±8 counts CD, shock x/c ±0.02</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2030,7 +2030,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Mesh Convergence / Grid Convergence Index Study</t>
+          <t>Grid Convergence Study (GCI)</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2040,12 +2040,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Three-level grid refinement study (12M/34M/96M cells) at M=0.85, α=2 deg to quantify discretization error via GCI estimates on CL, CD, and shock position.</t>
+          <t>Three unstructured grids (12M, 34M, 96M cells) assessed at M=0.85, α=2 deg; GCI computed for CL, CD, and shock x/c; monotonic refinement confirmed.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / GCI framework</t>
+          <t>Richardson extrapolation / GCI methodology</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>GCI: CL 0.9%, CD 3.5 counts, shock x/c within 0.015; refinement from 34M to 96M monotonic</t>
+          <t>GCI: CL 0.9%, CD 3.5 counts, shock x/c within 0.015; refinement 34M→96M monotonic in CL/CD</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2072,7 +2072,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Code Verification — Manufactured Solution and Regression Suite</t>
+          <t>Numerical Code Verification (MMS and Regression)</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Local manufactured-solution (source term) test on FUN3D 13.8; observed order of accuracy measured; full regression suite re-executed.</t>
+          <t>Local manufactured-solution (source term) test verified observed order of accuracy; FUN3D regression suite re-run; 2D NACA0012 inviscid grid-convergence test performed.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>FUN3D internal baseline and analytical order-of-accuracy expectation (~2nd order)</t>
+          <t>FUN3D internal manufactured-solution baseline; regression test suite reference values</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>Observed order 1.97 on smooth field; regression suite max diff &lt;1e-13; 2D NACA0012 inviscid grid-convergence recovered ~2nd-order lift trend</t>
+          <t>Observed order 1.97 on smooth field; regression suite max diff &lt;1e-13; 2D NACA0012 recovered ~2nd-order lift trend</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2109,7 +2109,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Input Uncertainty Propagation (LHS)</t>
+          <t>Solver Convergence Monitoring</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2119,27 +2119,22 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>40-point Latin hypercube sampling over α, turbulence intensity, and surface roughness to produce 95% prediction intervals and Sobol sensitivity indices on model outputs.</t>
+          <t>Residual drop and force history levelness monitored for all steady RANS runs; IDDES time-step sensitivity checked.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Decision tolerance bounds</t>
+          <t>Internal convergence criteria</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>Latin hypercube sampling, Sobol sensitivity indices</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>95% intervals: CL ±1.2% (within ±1.5% tolerance), CD ±8 counts (at boundary), shock x/c ±0.02 (at boundary); α explains ~72% of CL variance</t>
+          <t>Residuals dropped 4–5 orders; force histories level; time-step halving changed CL by 0.2%; IDDES 2000 physical timesteps with CFLconv ~3–5</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2151,7 +2146,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>DPW Community Benchmark Cross-Check</t>
+          <t>Community Benchmark Track Record (DPW)</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2161,7 +2156,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>FUN3D workflow compared against AIAA Drag Prediction Workshop community results from prior X-59 and TCA efforts to establish track record.</t>
+          <t>FUN3D workflow compared to AIAA Drag Prediction Workshop community results in prior X-59 and TCA efforts.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -2176,7 +2171,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>FUN3D matched community spread: lift ±1–2%, drag ±5–10 counts</t>
+          <t>Results within typical community spreads: lift ±1–2%, drag ±5–10 counts</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2330,12 +2325,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Software version controlled, regression tested, and builds reproducible with documented compiler environment.</t>
+          <t>Software is version-controlled, regression-tested, and reproducibly built with documented environment.</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>FUN3D 13.8 identified by git commit (3b7d9d1); full regression suite re-executed with max diff &lt;1e-13; deterministic MPI reduction and fixed random seeds for IDDES; Intel oneAPI 2023.2 / OpenMPI 4.1.5 build environment documented on Pleiades; run manifests with hashes and compiler flags archived on DAAC with nightly backups; git-tracked inputs and meshes; naming conventions and analysis plan (AL-23-CRM Rev C) documented.</t>
+          <t>FUN3D 13.8 at specific git commit (3b7d9d1) with Intel oneAPI 2023.2 and OpenMPI 4.1.5 on Pleiades. Full regression suite re-run with max diff &lt;1e-13. Git-tracked inputs and meshes; run manifests with hashes and compiler flags stored with checksums archived on DAAC with nightly backups. Deterministic MPI reduction enabled; fixed random seeds for IDDES. Two reruns of same IDDES case matched to within 0.3% on CL. Prior DPW benchmark participation demonstrates community-level pedigree. Team completed FUN3D user training in 2025.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2364,12 +2359,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Code demonstrates correct order of accuracy via manufactured solution or benchmark comparison.</t>
+          <t>Code correctly solves governing equations at expected order of accuracy.</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Local manufactured-solution (source term) test reproduced FUN3D internal baseline with observed order 1.97 (~2nd order as expected for the spatial discretization); 2D NACA0012 inviscid grid-convergence recovered ~2nd-order lift trend; full regression suite passed with max diff &lt;1e-13. Multiple independent checks confirm correct numerical implementation.</t>
+          <t>Local manufactured-solution (source term) test reproduced FUN3D internal baseline with observed order 1.97 on a smooth field. Regression suite max diff &lt;1e-13. 2D NACA0012 inviscid grid-convergence test recovered approximately 2nd-order lift trend. These collectively confirm second-order spatial accuracy of the solver.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2398,12 +2393,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>GCI or equivalent demonstrates discretization error is within decision tolerance contribution.</t>
+          <t>Discretization error quantified and shown to be within acceptable bounds for the QoIs.</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three-level unstructured grid refinement (12M/34M/96M cells) performed at M=0.85, α=2 deg. GCI estimates: CL 0.9%, CD 3.5 counts, shock x/c 0.015 — all well within decision tolerances. Refinement from 34M to 96M monotonic in CL/CD. Near-wall y+ ≤1 over 98% of surface area with growth ≤1.2. Time-step halving for IDDES changed CL by only 0.2%, confirming temporal convergence. Coarser-grid y+ histogram provided to red-team reviewers.</t>
+          <t>Three unstructured grids (12M, 34M, 96M cells) run at M=0.85, α=2 deg. GCI estimates: CL 0.9%, CD 3.5 counts, shock x/c within 0.015. Near-wall y+≤1 over 98% of area; first-layer height 1e-5 m, growth rate ≤1.2. Refinement from 34M→96M monotonic in CL/CD. Time-step halving for IDDES changed CL by only 0.2%. GCI values are well below the agreed decision tolerances.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2432,12 +2427,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residuals demonstrate adequate iterative convergence; force histories confirm solution stationarity.</t>
+          <t>Iterative residuals converged to sufficient levels; force quantities fully settled.</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Residuals dropped 4–5 orders of magnitude; force coefficient histories confirmed level (stationary). For IDDES: 2000 physical timesteps with CFLconv ~3–5 after initial transients. Restart from three different initial fields converged to the same steady RANS solution, confirming uniqueness of converged state. No negative volumes or CFL blowups reported; platform node health nominal.</t>
+          <t>Residuals dropped 4–5 orders of magnitude for all steady RANS runs. Force histories confirmed level before sampling. IDDES run for 2000 physical timesteps with CFLconv ~3–5 after initial transients. Restart from three different initial fields converged to the same steady RANS solution, confirming solution uniqueness. No negative volumes or CFL blowups reported.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2466,12 +2461,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent review confirms correct model setup, boundary conditions, and post-processing.</t>
+          <t>Model setup independently reviewed; boundary conditions and geometry verified; post-processing checked.</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Standard pre/post checklists applied by analyst team (FUN3D training completed 2025); peer desk check performed on setup prior to production runs; red-team review by AeroSci Branch (R. Jensen, L. Park, 2026-07-22) examined coarser-grid y+ histogram and BC summary — both items addressed; geometry planform/section verified vs. reference within 0.2 mm; farfield radius ≥20 chords and outlet nonreflecting confirmed; all plots scripted (Py3.11, Matplotlib) for reproducibility; run matrix RM-CRM-09 documented.</t>
+          <t>Standard pre/post checklists used; peer desk check performed before long runs. Independent red-team review by AeroSci Branch (R. Jensen, L. Park) on 2026-07-22 identified issues (coarser-grid y+ histogram and BC summary) which were subsequently addressed. Geometry verified against reference within 0.2 mm. Farfield radius ≥20 chords; nonreflecting outlet BC. All plots scripted in Python 3.11/Matplotlib for reproducibility. Analysis plan AL-23-CRM Rev C and run matrix RM-CRM-09 documented. Naming convention and DOIs reserved for final datasets.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2500,12 +2495,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equation choices and turbulence model selection are justified and limitations documented.</t>
+          <t>Governing equations and turbulence model selection justified for the physics regime; known limitations documented.</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Compressible steady RANS with k-ω SST selected; fully turbulent boundary layers consistent with NTF roughness strips and tripping (transition not modeled — stated as consistent with test conditions). Adiabatic no-slip walls, Sutherland's law for viscosity. Limitations explicitly documented: no aeroelastic coupling, fully turbulent assumption, no ice/contamination, RANS accuracy degrades above α≈5 deg with stronger separation. IDDES used only as qualitative guidance for buffet onset outside the formal envelope. Shock position sensitivity to βkω toggles checked (&lt;0.01c change). No turbulence constant tuning performed. Governing equations are standard and well-established for transonic attached-flow regime.</t>
+          <t>Compressible steady RANS with k-ω SST selected and justified for mean transonic loads; fully turbulent assumption consistent with NTF roughness strips and tripping. IDDES used for limited unsteady buffet spot checks at M=0.85, α=3 deg. Limitations explicitly documented: no aeroelastic or aero-thermal coupling, no ice/contamination modeling, RANS accuracy degrades above α≈5 deg with stronger separation. No tuning of turbulence constants performed; βkω sensitivity checked (&lt;0.01c shock shift). Adiabatic no-slip walls; Sutherland's law for thermodynamic properties. Sobol screening used to confirm dominant physics drivers (α ~72% of CL variance, Tu ~18%).</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2534,12 +2529,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Boundary conditions and material properties are traceable to measurements with quantified uncertainty.</t>
+          <t>Key model inputs characterized with measured uncertainties; boundary conditions traceable to facility measurements.</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>α from model attitude sensors ±0.03 deg (1σ); tunnel total conditions from facility DAS: p0 ±0.1%, T0 ±0.15%; turbulence intensity set to 0.5% ±0.3%; NIST air properties used; Sutherland constant validated to within ±2% over 200–300 K; geometry from LaRC CAD verified within 0.2 mm. Sobol screening identifies α as dominant input (72% of CL variance), Tu contributing 18%, roughness negligible — uncertainty sources are ranked and characterized. Input uncertainty ranges used in 40-point LHS propagation.</t>
+          <t>AoA from model attitude sensors: ±0.03 deg (1σ). Tunnel total conditions from facility DAS: p0 ±0.1%, T0 ±0.15%. Turbulence intensity set to 0.5% ±0.3%. NIST air properties used; Sutherland constant validated to within ±2% over 200–300 K. Geometry verified to within 0.2 mm of reference. Wall roughness set to NTF-equivalent smooth; roughness sensitivity checked. 40-point Latin hypercube spanning α ±0.05 deg, Tu 0.2–1.0%, roughness k+ 0–3 used to propagate input uncertainty to outputs.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2568,12 +2563,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article is representative of the modeled geometry with documented configuration control.</t>
+          <t>Experimental data from a well-characterized, production-relevant test article.</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>NTF CRM campaign uses the NASA CRM wing-body baseline (DPW-III/IV lineage), a well-documented community reference configuration. Blockage and weight corrections applied per facility procedures. The dataset has broad community use and traceability. However, number of independent test articles or repeat configurations is not explicitly stated in the memo; the dataset is treated as a single well-characterized reference campaign.</t>
+          <t>NTF CRM campaign from the AIAA DPW-III/IV lineage uses the standard NASA CRM wing-body model, a widely used community benchmark. Blockage and weight corrections applied per facility procedures. The test article geometry matches the computational model (Rev 2 CAD). No explicit sample-size justification or multiple-specimen statistical characterization reported, as is typical for large wind tunnel campaigns with a single primary model. AoA repeatability ±0.02 deg documented.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2602,12 +2597,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions are controlled and measured with calibrated instruments; measurement uncertainties are quantified.</t>
+          <t>Test conditions well-controlled, instruments calibrated, and measurement uncertainties quantified.</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>NTF cryogenic facility; measurement uncertainties explicitly stated: CL ±0.002, CD ±3 counts, Cp taps ±50 Pa, AoA repeatability ±0.02 deg; blockage/weight corrections per facility procedures; facility DAS for total conditions with p0 ±0.1%, T0 ±0.15%. Conditions span M=0.85, α=2–4 deg within the validated envelope. Test conditions match the intended COU physics regime (transonic, attached boundary layer with trip).</t>
+          <t>NTF cryogenic facility with calibrated instruments. Measurement uncertainties explicitly stated: CL ±0.002, CD ±3 counts, Cp taps ±50 Pa, AoA repeatability ±0.02 deg. Total conditions from facility DAS: p0 ±0.1%, T0 ±0.15%. Blockage and weight corrections applied per facility procedures. Turbulence intensity characterized at 0.5% ±0.3%. Facility is a recognized national test facility with established quality processes (DPW lineage).</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2636,12 +2631,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>CFD boundary conditions demonstrably matched to tunnel test conditions with uncertainty propagation.</t>
+          <t>Computational model inputs match experimental conditions with propagated uncertainties.</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Farfield pressure and temperature set to target M and Re matching NTF conditions; α applied via velocity vector using calibrated attitude sensor values (±0.03 deg); roughness set to NTF-equivalent smooth; tunnel turbulence intensity matched (0.5% ±0.3%); input parameter comparison explicitly performed and sensitivity to each input quantified via Sobol indices. LHS propagation uses the measured uncertainty ranges of the experimental inputs. Boundary condition summary provided to and reviewed by red-team.</t>
+          <t>Farfield pressure and temperature set directly from facility DAS to match target M and Re. AoA set via velocity vector matching calibrated model attitude sensors. Wall roughness matched to NTF-equivalent smooth configuration. Sutherland constants validated against NIST air over the relevant temperature range. 40-point LHS propagation explicitly links input uncertainties (α, Tu, roughness) measured in the tunnel to output prediction intervals, providing quantified equivalency of input parameters.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2670,12 +2665,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of model predictions to experimental data against agreed decision tolerances at multiple operating points.</t>
+          <t>Quantitative comparison metrics for all QoIs at multiple operating conditions; results within agreed tolerances.</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>At M=0.85, α=2–4 deg: CL within 0.8% (tolerance ±1.5% — passed); CD within 6 counts (tolerance ±8 counts — passed); spanwise shock position within 0.02c (tolerance ±0.02c — at boundary, passed); Cp RMS within 3–4% at upper-surface tap rows (tolerance ±5% — passed). 95% prediction intervals from LHS: CL ±1.2%, CD ±8 counts, shock x/c ±0.02 — within or at decision tolerances. Multiple comparison points across α sweep. DPW community benchmark cross-check provides additional independent comparison context.</t>
+          <t>Validation at M=0.85, α=2–4 deg: CL within 0.8% (tolerance ±1.5%), CD within 6 counts (tolerance ±8 counts), shock x/c within 0.02c (tolerance ±0.02c), Cp RMS within 3–4% on upper-surface rows (tolerance ±5%). All QoIs pass agreed decision tolerances. 95% prediction intervals from LHS: ±1.2% CL, ±8 counts CD, shock x/c ±0.02 — at or within tolerances. Prior DPW benchmarks provide additional community-level comparison data (lift ±1–2%, drag ±5–10 counts). Multiple spanwise tap rows assessed.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2704,12 +2699,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs (CL, CD, Cp, shock position) directly address the loads envelope sizing decision and are measurable both computationally and experimentally.</t>
+          <t>Model QoIs directly address the loads-envelope decision need and are measurable both computationally and experimentally.</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>QoIs are CL, CD, sectional Cp, and shock position — exactly the quantities required for aero loads and shock positioning in structural loads envelope sizing. Decision tolerances are agreed with Loads/Structures stakeholders (≤±1.5% CL, ≤±8 drag counts, shock ±0.02c, Cp RMS ±5%). All QoIs are directly measurable in NTF with calibrated instruments and computed by FUN3D at the same operating conditions. Sobol analysis confirms that output variance is dominated by physically meaningful inputs.</t>
+          <t>The QoIs (CL, CD, sectional Cp, shock x/c) are exactly the quantities required by Loads/Structures for the aero loads envelope decision. Decision tolerances (±1.5% CL, ±8 drag counts, ±0.02c shock, ±5% Cp RMS) were agreed with the end users. All QoIs are directly measurable in both the NTF experiment (force balance, Cp taps) and the CFD simulation (integrated forces, surface solution). Shock position is assessed at both computational and experimental levels via Cp gradients.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2738,12 +2733,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions span the COU envelope (M=0.72–0.90, α=0–4 deg, Re=3–8M) or gaps are documented with justified extrapolation.</t>
+          <t>Validation conditions cover the intended use envelope; gaps are documented with appropriate limitations.</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation data explicitly covers M=0.85, α=2–4 deg — a subset of the full COU envelope (M=0.72–0.90, α=0–4 deg, Re=3–8M). The memo does not present explicit validation comparisons at Mach numbers below 0.85 or at α=0–2 deg, representing a partial coverage gap. However, the NTF dataset has DPW-III/IV lineage (community standard), the geometry is identical, physics regime is the same (attached transonic RANS), and limits of use are explicitly documented (model not trusted above α≈5 deg). DPW community benchmarks provide supplementary evidence across the broader Mach range. Gap acknowledged; IDDES use outside formal envelope explicitly restricted to qualitative guidance only.</t>
+          <t>Validation performed at M=0.85, α=2–4 deg using NTF CRM data matching the intended geometry and flow regime. COU envelope is M=0.72–0.90, α=0–4 deg, Re=3–8M. Validation coverage is demonstrated at the upper Mach and midrange angle-of-attack; the full Mach range (0.72–0.84) and α=0–1 deg are not explicitly validated in the reported results, representing a modest gap. Limitations at α&gt;5 deg explicitly documented. IDDES results for unsteady buffet (M=0.85, α=3 deg) provided only as qualitative guidance with no formal margins. Use outside the stated envelope is explicitly prohibited. The DPW benchmark track record provides additional supporting evidence across the Mach range.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2928,7 +2923,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>All 13 credibility factors meet or exceed required levels for an MRL 3 / Medium assurance application. Steady RANS predictions satisfy all agreed decision tolerances (CL within 0.8% vs. ±1.5% limit, CD within 6 counts vs. ±8 count limit, shock position within 0.02c, Cp RMS within 3–4% vs. ±5% limit) at the primary validation conditions. Discretization error (GCI CL 0.9%, CD 3.5 counts) is within tolerance. Input uncertainties are propagated and 95% intervals remain within decision bounds. Code is version-controlled and regression-tested. Independent red-team review (Jensen, Park, 2026-07-22) was completed and findings addressed. Limitations are documented: use restricted to M=0.72–0.90, α=0–4 deg, Re=3–8M; IDDES results are accepted only as qualitative guidance for buffet onset with no formal margins derived from unsteady runs. Partial Mach/alpha coverage of validation data relative to the full COU envelope is noted but mitigated by community DPW benchmark evidence, consistent geometry and physics regime, and explicit limits-of-use documentation.</t>
+          <t>The FUN3D steady RANS model meets all agreed decision tolerances across the primary validation conditions (CL within 0.8% vs. ±1.5% limit, CD within 6 counts vs. ±8 count limit, shock x/c within 0.02c, Cp RMS within 3–4% vs. ±5% limit). Discretization error (GCI) and input uncertainties are quantified and propagated; 95% prediction intervals are within or at tolerance bounds. All 13 credibility factors achieve levels commensurate with the MRL 3 assessment. Software QA, code verification, numerical convergence, and independent review are well-documented. Use is approved for steady RANS predictions within the validated envelope (M=0.72–0.90, α=0–4 deg, Re=3–8M) for loads envelope support. IDDES results are approved only as qualitative guidance for buffet onset; no formal margins are to be derived from unsteady runs. Use outside the validated envelope is explicitly prohibited. Final sign-off targeted for SRR-2.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2938,7 +2933,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>M. Rivera, CFD V&amp;V Lead</t>
+          <t>M. Rivera, CFD V&amp;V Lead (with red-team endorsement by R. Jensen and L. Park, AeroSci Branch)</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
